--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488086_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488086_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5123</v>
+        <v>4.026</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2263</v>
+        <v>3.5154</v>
       </c>
       <c r="F2" t="n">
-        <v>0.286</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>2.1645</v>
@@ -610,13 +610,13 @@
         <v>1.1893</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7569</v>
+        <v>-0.2432</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5688</v>
+        <v>-0.2798</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1881</v>
+        <v>0.0365</v>
       </c>
       <c r="V2" t="n">
         <v>0.9154</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6787</v>
+        <v>1.0868</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0224</v>
+        <v>0.3685</v>
       </c>
       <c r="F3" t="n">
-        <v>1.701</v>
+        <v>0.7183</v>
       </c>
       <c r="G3" t="n">
         <v>2.8372</v>
@@ -688,13 +688,13 @@
         <v>1.3876</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3063</v>
+        <v>-0.2855</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.756</v>
+        <v>-0.3651</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0623</v>
+        <v>0.0795</v>
       </c>
       <c r="V3" t="n">
         <v>-0.8701</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3636</v>
+        <v>0.8181</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7191</v>
+        <v>-0.798</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0827</v>
+        <v>1.6162</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3983</v>
@@ -766,13 +766,13 @@
         <v>1.784</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2887</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1393</v>
+        <v>-0.2182</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.1495</v>
+        <v>-0.616</v>
       </c>
       <c r="V4" t="n">
         <v>0.2666</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. CHEKRI KOURAYCHE</t>
+          <t>W. EL OTMANI MOHAMED</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1782</v>
+        <v>-0.7065</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1841</v>
+        <v>-0.3868</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9941</v>
+        <v>-0.3197</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7903</v>
+        <v>0.9855</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9184</v>
+        <v>1.6245</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.128</v>
+        <v>-0.639</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6178</v>
+        <v>2.0162</v>
       </c>
       <c r="K7" t="n">
-        <v>2.4421</v>
+        <v>2.6836</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8243</v>
+        <v>-0.6675</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1726</v>
+        <v>-1.0306</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-1.0591</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6962</v>
+        <v>0.0285</v>
       </c>
       <c r="P7" t="n">
-        <v>-4.1627</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.9556</v>
+        <v>-2.9733</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7929</v>
+        <v>1.3876</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4968</v>
+        <v>-0.6846</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4134</v>
+        <v>-0.6367</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0834</v>
+        <v>-0.0479</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3027</v>
+        <v>0.5784</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7403</v>
+        <v>1.2071</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.0429</v>
+        <v>-0.6287</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W. EL OTMANI MOHAMED</t>
+          <t>M. GAMEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2179</v>
+        <v>-1.2877</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1228</v>
+        <v>-2.5855</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0951</v>
+        <v>1.2978</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9855</v>
+        <v>-1.5958</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6245</v>
+        <v>1.5531</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.639</v>
+        <v>-3.1489</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0162</v>
+        <v>-2.0264</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6836</v>
+        <v>0.7264</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6675</v>
+        <v>-2.7528</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0306</v>
+        <v>0.4307</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0591</v>
+        <v>0.8267</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0285</v>
+        <v>-0.3961</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5858</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3876</v>
+        <v>0.5947</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.196</v>
+        <v>0.1009</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3727</v>
+        <v>-0.1715</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1767</v>
+        <v>0.2724</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5784</v>
+        <v>0.6036</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2071</v>
+        <v>0.6036</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6287</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. GAMEZ SANCHEZ</t>
+          <t>F. CHEKRI KOURAYCHE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2826</v>
+        <v>-2.272</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6084</v>
+        <v>-0.7724</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3258</v>
+        <v>-1.4995</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5958</v>
+        <v>1.7903</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5531</v>
+        <v>1.9184</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.1489</v>
+        <v>-0.128</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.0264</v>
+        <v>1.6178</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7264</v>
+        <v>2.4421</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.7528</v>
+        <v>-0.8243</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4307</v>
+        <v>0.1726</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8267</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3961</v>
+        <v>0.6962</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3964</v>
+        <v>-4.1627</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9911</v>
+        <v>-4.9556</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5947</v>
+        <v>0.7929</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1061</v>
+        <v>1.4031</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1944</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3005</v>
+        <v>0.578</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6036</v>
+        <v>-1.3027</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6036</v>
+        <v>1.7403</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-3.0429</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4946</v>
+        <v>-3.0224</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4681</v>
+        <v>-2.4452</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0265</v>
+        <v>-0.5772</v>
       </c>
       <c r="G10" t="n">
         <v>0.0141</v>
@@ -1234,13 +1234,13 @@
         <v>0.5947</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6475</v>
+        <v>-0.1753</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1944</v>
+        <v>-0.1715</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4531</v>
+        <v>-0.0038</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4737</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.291</v>
+        <v>-6.2472</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.9595</v>
+        <v>-4.1403</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3315</v>
+        <v>-2.1069</v>
       </c>
       <c r="G11" t="n">
         <v>-2.644</v>
@@ -1312,13 +1312,13 @@
         <v>1.5858</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4742</v>
+        <v>-0.4304</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2351</v>
+        <v>0.0543</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7093</v>
+        <v>-0.4847</v>
       </c>
       <c r="V11" t="n">
         <v>-2.7763</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.313299999999998</v>
+        <v>-8.008500000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.8581</v>
+        <v>-7.244299999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4552999999999998</v>
+        <v>-0.7639999999999998</v>
       </c>
       <c r="G12" t="n">
         <v>3.0215</v>
@@ -1360,7 +1360,7 @@
         <v>7.624500000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.602799999999999</v>
+        <v>-4.6028</v>
       </c>
       <c r="J12" t="n">
         <v>3.3651</v>
@@ -1372,7 +1372,7 @@
         <v>-3.6873</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3431999999999997</v>
+        <v>-0.3431999999999998</v>
       </c>
       <c r="N12" t="n">
         <v>0.5723</v>
@@ -1390,13 +1390,13 @@
         <v>9.316600000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7257</v>
+        <v>-1.4208</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.5771</v>
+        <v>-0.9634</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1487000000000001</v>
+        <v>-0.4576000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-4.0588</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.8626</v>
+        <v>5.3799</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1827</v>
+        <v>1.6547</v>
       </c>
       <c r="F13" t="n">
-        <v>4.6799</v>
+        <v>3.7253</v>
       </c>
       <c r="G13" t="n">
         <v>1.5918</v>
@@ -1468,13 +1468,13 @@
         <v>2.3787</v>
       </c>
       <c r="S13" t="n">
-        <v>4.8586</v>
+        <v>2.3759</v>
       </c>
       <c r="T13" t="n">
-        <v>2.992</v>
+        <v>1.4639</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8667</v>
+        <v>0.912</v>
       </c>
       <c r="V13" t="n">
         <v>2.0068</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>P. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0917</v>
+        <v>4.9569</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5495</v>
+        <v>4.4214</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5422</v>
+        <v>0.5355</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.1388</v>
+        <v>1.0728</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.9729</v>
+        <v>-1.847</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8341</v>
+        <v>2.9198</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.3834</v>
+        <v>2.379</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.712</v>
+        <v>-1.0556</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6713</v>
+        <v>3.4346</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2446</v>
+        <v>-1.3062</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2609</v>
+        <v>-0.7914</v>
       </c>
       <c r="O14" t="n">
-        <v>1.5055</v>
+        <v>-0.5148</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9822</v>
+        <v>2.1805</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9822</v>
+        <v>2.1805</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3542</v>
+        <v>1.0297</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0145</v>
+        <v>0.8353</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3687</v>
+        <v>0.1944</v>
       </c>
       <c r="V14" t="n">
-        <v>2.894</v>
+        <v>0.674</v>
       </c>
       <c r="W14" t="n">
-        <v>2.9474</v>
+        <v>1.2071</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.0533</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ SANCHEZ</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8964</v>
+        <v>4.4607</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8101</v>
+        <v>2.0589</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0863</v>
+        <v>2.4018</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0728</v>
+        <v>-1.1388</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.847</v>
+        <v>-1.9729</v>
       </c>
       <c r="I15" t="n">
-        <v>2.9198</v>
+        <v>0.8341</v>
       </c>
       <c r="J15" t="n">
-        <v>2.379</v>
+        <v>-1.3834</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.0556</v>
+        <v>-0.712</v>
       </c>
       <c r="L15" t="n">
-        <v>3.4346</v>
+        <v>-0.6713</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3062</v>
+        <v>0.2446</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7914</v>
+        <v>-1.2609</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5148</v>
+        <v>1.5055</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1805</v>
+        <v>1.9822</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1805</v>
+        <v>1.9822</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0308</v>
+        <v>0.7232</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2241</v>
+        <v>0.4949</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2548</v>
+        <v>0.2283</v>
       </c>
       <c r="V15" t="n">
-        <v>0.674</v>
+        <v>2.894</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2071</v>
+        <v>2.9474</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5331</v>
+        <v>-0.0533</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. RAGA RODRIGUEZ</t>
+          <t>P. CARRASCO LOBO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4784</v>
+        <v>1.6794</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0556</v>
+        <v>1.1919</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4228</v>
+        <v>0.4875</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4494</v>
+        <v>1.342</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0113</v>
+        <v>0.2554</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4381</v>
+        <v>1.0866</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2301</v>
+        <v>1.5167</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0694</v>
+        <v>0.7131</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1607</v>
+        <v>0.8036</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2193</v>
+        <v>-0.1747</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0581</v>
+        <v>-0.4577</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2774</v>
+        <v>0.2831</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1893</v>
+        <v>1.5858</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.784</v>
+        <v>1.5858</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8219</v>
+        <v>-0.0413</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7988</v>
+        <v>-0.3247</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0231</v>
+        <v>0.2835</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6036</v>
+        <v>-1.2071</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6036</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.168</v>
+        <v>1.456</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3103</v>
+        <v>-0.1065</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4783</v>
+        <v>1.5625</v>
       </c>
       <c r="G17" t="n">
         <v>0.3803</v>
@@ -1780,13 +1780,13 @@
         <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6743</v>
+        <v>-0.3864</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7891</v>
+        <v>-0.5854</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1148</v>
+        <v>0.199</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1237</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. CARRASCO LOBO</t>
+          <t>L. MORENO MORALES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.984</v>
+        <v>0.9063</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5807</v>
+        <v>-0.5401</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4032</v>
+        <v>1.4464</v>
       </c>
       <c r="G18" t="n">
-        <v>1.342</v>
+        <v>0.0372</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2554</v>
+        <v>-0.9577</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0866</v>
+        <v>0.9949</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5167</v>
+        <v>0.0122</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7131</v>
+        <v>-1.2372</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8036</v>
+        <v>1.2494</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1747</v>
+        <v>0.025</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4577</v>
+        <v>0.2795</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2831</v>
+        <v>-0.2545</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5858</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5858</v>
+        <v>0.9911</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7367</v>
+        <v>0.0496</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.3808</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1992</v>
+        <v>0.4303</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2071</v>
+        <v>1.8107</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.8107</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. VERKERK</t>
+          <t>R. RAGA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7503</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1494</v>
+        <v>-0.9631</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6009</v>
+        <v>1.507</v>
       </c>
       <c r="G19" t="n">
-        <v>1.489</v>
+        <v>1.4494</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3208</v>
+        <v>1.0113</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8098</v>
+        <v>0.4381</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9296</v>
+        <v>1.2301</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6802</v>
+        <v>1.0694</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2494</v>
+        <v>0.1607</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4406</v>
+        <v>0.2193</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.001</v>
+        <v>-0.0581</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5604</v>
+        <v>0.2774</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5858</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9822</v>
+        <v>-2.9733</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3964</v>
+        <v>1.784</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9004</v>
+        <v>0.8874</v>
       </c>
       <c r="T19" t="n">
-        <v>0.202</v>
+        <v>0.7801</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6984</v>
+        <v>0.1073</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0533</v>
+        <v>-0.6036</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.0533</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. MORENO MORALES</t>
+          <t>J. VERKERK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4041</v>
+        <v>0.35</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8457</v>
+        <v>-0.0543</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2498</v>
+        <v>0.4044</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0372</v>
+        <v>1.489</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9577</v>
+        <v>-0.3208</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9949</v>
+        <v>1.8098</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0122</v>
+        <v>1.9296</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2372</v>
+        <v>0.6802</v>
       </c>
       <c r="L20" t="n">
         <v>1.2494</v>
       </c>
       <c r="M20" t="n">
-        <v>0.025</v>
+        <v>-0.4406</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2795</v>
+        <v>-1.001</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2545</v>
+        <v>0.5604</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9911</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9911</v>
+        <v>0.3964</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4526</v>
+        <v>0.5001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6864</v>
+        <v>-0.0017</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2338</v>
+        <v>0.5019</v>
       </c>
       <c r="V20" t="n">
-        <v>1.8107</v>
+        <v>-0.0533</v>
       </c>
       <c r="W20" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.0533</v>
       </c>
     </row>
     <row r="21">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2301</v>
+        <v>-1.8964</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4408</v>
+        <v>-1.1352</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7893</v>
+        <v>-0.7612</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6019</v>
@@ -2170,13 +2170,13 @@
         <v>0.3964</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4915</v>
+        <v>-0.1578</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1027</v>
+        <v>0.2029</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3888</v>
+        <v>-0.3607</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5331</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9015</v>
+        <v>-3.1124</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2814</v>
+        <v>-1.6889</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6201</v>
+        <v>-1.4235</v>
       </c>
       <c r="G23" t="n">
         <v>-2.1592</v>
@@ -2248,13 +2248,13 @@
         <v>0.3964</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4819</v>
+        <v>-0.6928</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2972</v>
+        <v>-0.7046</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1847</v>
+        <v>0.0118</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6569</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.0539</v>
+        <v>-5.2743</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.4515</v>
+        <v>-3.8403</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6024</v>
+        <v>-1.434</v>
       </c>
       <c r="G24" t="n">
         <v>-5.1609</v>
@@ -2326,13 +2326,13 @@
         <v>1.1893</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3046</v>
+        <v>-0.5249</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1414</v>
+        <v>-0.5302</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1631</v>
+        <v>0.0053</v>
       </c>
       <c r="V24" t="n">
         <v>0.2133</v>
@@ -2362,10 +2362,10 @@
         <v>9.752700000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>1.300999999999999</v>
+        <v>1.3012</v>
       </c>
       <c r="F25" t="n">
-        <v>8.451599999999999</v>
+        <v>8.451699999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-2.3956</v>
@@ -2395,7 +2395,7 @@
         <v>3.5669</v>
       </c>
       <c r="P25" t="n">
-        <v>3.964399999999999</v>
+        <v>3.9644</v>
       </c>
       <c r="Q25" t="n">
         <v>-10.9021</v>
@@ -2407,10 +2407,10 @@
         <v>3.7627</v>
       </c>
       <c r="T25" t="n">
-        <v>1.2496</v>
+        <v>1.2497</v>
       </c>
       <c r="U25" t="n">
-        <v>2.513300000000001</v>
+        <v>2.5131</v>
       </c>
       <c r="V25" t="n">
         <v>4.4211</v>
